--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等不用句号的语言在项目档案关闭本项（nrc-th）。</t>
+          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等不用句号的语言在语言层默认关闭本项（languages/th.json）。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；projects/nrc-th/checks.json（关闭）；清单文档</t>
+          <t>scripts/lqe_io.py；languages/th.json（默认关）；清单文档</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">

--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等不用句号的语言在语言层默认关闭本项（languages/th.json）。</t>
+          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等无句号体系语言由语言属性（languages/th.json：sentence_terminator=none）自动判定不适用，无需逐项目配置。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；languages/th.json（默认关）；清单文档</t>
+          <t>scripts/lqe_io.py；languages/th.json（属性自动判定）；清单文档</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">

--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -594,12 +594,12 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等无句号体系语言由语言属性（languages/th.json：sentence_terminator=none）自动判定不适用，无需逐项目配置。</t>
+          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等无句号体系语言由语言属性（languages/th/：sentence_terminator=none）自动判定不适用，无需逐项目配置。</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；languages/th.json（属性自动判定）；清单文档</t>
+          <t>scripts/lqe_io.py；languages/th/（属性自动判定）；清单文档</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">

--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>现行 projects/&lt;名&gt;/checks.json 的 custom 正则已实现「按项目喂正则」，但仅支持单边命中报错，无法做源↔译对账。扩展：custom 增加 type 字段——search（现状，单边命中）／count_match（新增：正则在源、译分别取全部匹配，数量不等报 Markup Major），即可覆盖 &lt;color=&gt;、[b][/b] 等任意项目标签体系。燕云专属 #G…#E 内置项，其他项目以 "color_tags": false 关闭（机制已有）。标签嵌套、相对位置等复杂校验仍归 AI 评估。</t>
+          <t>现行 projects/&lt;game&gt;/&lt;lang&gt;/checks.json 的 custom 正则已实现「按项目喂正则」，但仅支持单边命中报错，无法做源↔译对账。扩展：custom 增加 type 字段——search（现状，单边命中）／count_match（新增：正则在源、译分别取全部匹配，数量不等报 Markup Major），即可覆盖 &lt;color=&gt;、[b][/b] 等任意项目标签体系。燕云专属 #G…#E 内置项，其他项目以 "color_tags": false 关闭（机制已有）。标签嵌套、相对位置等复杂校验仍归 AI 评估。</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>正则 \b(\w+)\s+\1\b 忽略大小写扫描译文；白名单豁免英文合法重复（had had／that that／no no／so so 等）；仅空格分词译文生效（泰语跳过——泰文表重复另有 ๆ 标记体系）；Grammar Minor；对话体重复由 AI 甄别。</t>
+          <t>正则 \b(\w+)\s+\1\b 忽略大小写扫描译文；白名单豁免英文合法重复（had had／that that／no no／so so 等）；仅空格分词语言生效，由语言属性 word_delim 自动判定（泰语自动跳过——泰文表重复另有 ๆ 标记体系）；Grammar Minor；对话体重复由 AI 甄别。</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">

--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -527,417 +527,424 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>需要 PM 动作的共 5 条（#2/#3/#5/#7/#10，见最后一列）；其余 5 条无需提供任何材料，批准即可实施</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>逐条修改报告</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>PM 建议</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>是否需要修改</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>修改程度</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>如何修改（实现方案与误报防控）</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>涉及文件</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>译文句号缺失（建议用 AI 识别源译句号数量是否对应）</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>部分需要</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>新增内置检查（拟编 N5，句尾子集）＋ AI 评估关注点（句中数量）</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等无句号体系语言由语言属性（languages/th/：sentence_terminator=none）自动判定不适用，无需逐项目配置。</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_io.py；languages/th/（属性自动判定）；清单文档</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>需要 PM 提供 / 拍板</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>中文数字对应（如「三次」→ 3/three）</t>
+          <t>译文句号缺失（建议用 AI 识别源译句号数量是否对应）</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>需要</t>
+          <t>部分需要</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>新增内置检查（拟编 N6）</t>
+          <t>新增内置检查（拟编 N5，句尾子集）＋ AI 评估关注点（句中数量）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>确定性解析即可、无需依赖 AI 识别：解析中文数字（〇一二…十百千万亿、两、第 N），仅「中文数字＋量词/单位」模式触发（次/个/名/位/层/级/天/秒/章/倍等），防「一起/三思/万一」类虚用成语误报；「一」默认豁免、仅强量词模式（一次/一名）触发。译侧接受阿拉伯数字或英文数词（one~hundred、first 等序数、once/twice）。报 Mistranslation Major；AI 评估可移除上下文误报（与现行数值检查同机制）。</t>
+          <t>句尾比对不必用 AI 计数，确定性代码即可：源文以「。！？…」结尾而译文句尾无终止标点（.!?…），或源文无句尾标点而译文擅自添加 → Punctuation Minor。句中句号不做 1:1 数量对账——中英句子合法拆合（一句中文译成两句英文）会大量误报，该部分写入 AI 评估关注点，由 AI 结合语义判断是否漏句。泰语等无句号体系语言由语言属性（languages/th/：sentence_terminator=none）自动判定不适用，无需逐项目配置。</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；清单文档</t>
+          <t>scripts/lqe_io.py；languages/th/（属性自动判定）；清单文档</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>「一」的触发范围（建议仅量词强模式）；泰语数词映射是否本期纳入</t>
+          <t>无需提供——批准即可实施</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>中文数字对应（如「三次」→ 3/three）</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>需要</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>新增内置检查（拟编 N6）</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>确定性解析即可、无需依赖 AI 识别：解析中文数字（〇一二…十百千万亿、两、第 N），仅「中文数字＋量词/单位」模式触发（次/个/名/位/层/级/天/秒/章/倍等），防「一起/三思/万一」类虚用成语误报；「一」默认豁免、仅强量词模式（一次/一名）触发。译侧接受阿拉伯数字或英文数词（one~hundred、first 等序数、once/twice）。报 Mistranslation Major；AI 评估可移除上下文误报（与现行数值检查同机制）。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py；清单文档</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>请拍板两件事：① 数字『一』要不要也查——查的话误报会变多，建议只查『一次/一名』这类带量词的；② 泰语版要不要这期一起做</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>标签（TAG）正则按项目单独配置（现内置仅燕云 #G…#E）</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>需要（方向正确，架构已支持一半）</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>扩展项目自定义检查架构（约 15 行）＋各项目配置</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>现行 projects/&lt;game&gt;/&lt;lang&gt;/checks.json 的 custom 正则已实现「按项目喂正则」，但仅支持单边命中报错，无法做源↔译对账。扩展：custom 增加 type 字段——search（现状，单边命中）／count_match（新增：正则在源、译分别取全部匹配，数量不等报 Markup Major），即可覆盖 &lt;color=&gt;、[b][/b] 等任意项目标签体系。燕云专属 #G…#E 内置项，其他项目以 "color_tags": false 关闭（机制已有）。标签嵌套、相对位置等复杂校验仍归 AI 评估。</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py；各项目 checks.json</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
-        <is>
-          <t>需 PM 提供各项目标签规格样例（正则由工程侧编写）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>小数点缺失</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>不需要</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>无需改动（已实现）</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>实测现行代码：数值一致性检查的提取正则 \d[\d,]*(?:\.\d+)? 将小数作为完整数值 token 处理——源「2.5」译成「25」「2,5」或缺失，均报「Source number missing/changed」（Mistranslation Major）。</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>无（可向 PM 演示用例）</t>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>请提供：每个项目的标签长什么样，每种标签贴几行原文例子即可（如 &lt;color=#FF0000&gt;文字&lt;/color&gt;、[b]文字[/b]），技术规则我们来写</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>小数点缺失</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>无需改动（已实现）</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>实测现行代码：数值一致性检查的提取正则 \d[\d,]*(?:\.\d+)? 将小数作为完整数值 token 处理——源「2.5」译成「25」「2,5」或缺失，均报「Source number missing/changed」（Mistranslation Major）。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>无需提供——已实现，需要的话可现场演示</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>异源同译（不同源文译成相同译文）</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>不需要新增设计</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>无需新增（已含于待批准 N2）；落码时补误报分档</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>清单 N2「同源异译」设计原文已含双向：「相同源文对应不同译文；以及相同译文对应不同源文」。落码时补充长度分档防误报：短词条（源 &lt;10 字符）合法收敛（确定/确认→Confirm）不报；较长文本（≥20 字符）异源同译高度可疑（复制错位/漏改），报 Inconsistency Minor；AI 甄别。</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py（随 N2 实施）</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>长度分档阈值（建议 20 字符）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>单词连续重复（如 the the）</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>需要</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>新增内置检查（拟编 N7）</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>正则 \b(\w+)\s+\1\b 忽略大小写扫描译文；白名单豁免英文合法重复（had had／that that／no no／so so 等）；仅空格分词语言生效，由语言属性 word_delim 自动判定（泰语自动跳过——泰文表重复另有 ๆ 标记体系）；Grammar Minor；对话体重复由 AI 甄别。</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>scripts/lqe_io.py；清单文档</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>请拍板：多长的句子译文完全相同才算可疑——建议 20 字以上才报，『确定/确认』这类短按钮词不报</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>特定术语大小写（HP/ATK/人名等必须大写）</t>
+          <t>单词连续重复（如 the the）</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>需要（实测现版漏检）</t>
+          <t>需要</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>扩展现有术语检查</t>
+          <t>新增内置检查（拟编 N7）</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>实测确认缺口：现行术语匹配统一转小写比对，HP 译成 hp 不报错。改法：不区分大小写命中译法后追加大小写校验——全大写缩写词条（≥2 字母：HP/ATK/SSR）及词内混合大小写词条要求精确匹配；首字母大写词条（人名）校验首字母。归类建议：默认 Company style Minor（Terminology 类被脚本强制 Major，全判将罚分膨胀），全大写缩写误写升 Major；亦可在术语表增加 case_sensitive 列显式控制。</t>
+          <t>正则 \b(\w+)\s+\1\b 忽略大小写扫描译文；白名单豁免英文合法重复（had had／that that／no no／so so 等）；仅空格分词语言生效，由语言属性 word_delim 自动判定（泰语自动跳过——泰文表重复另有 ๆ 标记体系）；Grammar Minor；对话体重复由 AI 甄别。</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；（可选）术语表加列</t>
+          <t>scripts/lqe_io.py；清单文档</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>归类与严重度分档需 PM 拍板；是否加 case_sensitive 列</t>
+          <t>无需提供——批准即可实施</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>同个词内大小写混乱（如 AppLe）</t>
+          <t>特定术语大小写（HP/ATK/人名等必须大写）</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>需要</t>
+          <t>需要（实测现版漏检）</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>新增内置检查（拟编 N8）</t>
+          <t>扩展现有术语检查</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>检测词内小写→大写转折（AppLe／heLLo）；豁免：术语表词条、Mc/Mac 前缀、iPhone 型单字母小写头、PvP 型缩写、标签/变量内容；Spelling Minor；剩余少量品牌词误报由 AI 甄别。</t>
+          <t>实测确认缺口：现行术语匹配统一转小写比对，HP 译成 hp 不报错。改法：不区分大小写命中译法后追加大小写校验——全大写缩写词条（≥2 字母：HP/ATK/SSR）及词内混合大小写词条要求精确匹配；首字母大写词条（人名）校验首字母。归类建议：默认 Company style Minor（Terminology 类被脚本强制 Major，全判将罚分膨胀），全大写缩写误写升 Major；亦可在术语表增加 case_sensitive 列显式控制。</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>scripts/lqe_io.py；清单文档</t>
+          <t>scripts/lqe_io.py；（可选）术语表加列</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>请拍板两件事：① 大小写写错算多重——建议一般情况算轻微错误，HP/ATK 这类全大写缩写写错算严重错误；② 要不要在术语表加一列，标出哪些词必须严格按表里的大小写</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>同个词内大小写混乱（如 AppLe）</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>需要</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>新增内置检查（拟编 N8）</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>检测词内小写→大写转折（AppLe／heLLo）；豁免：术语表词条、Mc/Mac 前缀、iPhone 型单字母小写头、PvP 型缩写、标签/变量内容；Spelling Minor；剩余少量品牌词误报由 AI 甄别。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>scripts/lqe_io.py；清单文档</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>无需提供——批准即可实施</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>成对标点不完整（半个引号/括号）</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>需要</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>新增内置检查（拟编 N9）</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>按对类计数比对：()、[]、「」、『』、“”、‘’，直双引号 " 按奇偶；仅「源侧配对完整而译侧不完整」报错——源文本身跨段半引号则跳过，防误报；直单引号 ' 默认豁免（英文撇号）；{} 不查（变量检查已覆盖）；Punctuation Minor。</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>scripts/lqe_io.py；清单文档</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>无需提供——批准即可实施</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>省略号样式按项目规定（…／...）</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>不需要改代码</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>仅项目配置（零代码）</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>正是现行 custom 正则的标准用例：要求「…」的项目加 pattern \.{3}（命中提示应使用…），要求「...」的项目加 pattern …；写入各项目 checks.json 即生效，类别/严重度可配（默认 Company style Minor）。</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t>各项目 checks.json</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>各项目省略号取向（按 SG/PM 确认后写入）</t>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>请告知：每个项目要用哪种省略号——『…』还是『...』，逐项目确认一次即可</t>
         </is>
       </c>
     </row>

--- a/docs/PM反馈检查项修改报告.xlsx
+++ b/docs/PM反馈检查项修改报告.xlsx
@@ -523,14 +523,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>状态：全部待批准；批准后落码，并同步《质量检查项清单》（md 与 xlsx）</t>
+          <t>状态：PM 已批准（2026-06-12）并全部实施——N5–N9、#3 通用标签对账+custom count_match、#7 缩写大小写（Major）、#10 省略号混用检查；#2 泰语数词已纳入；#5 的 20 字分档随 N2 实施线记录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>需要 PM 动作的共 5 条（#2/#3/#5/#7/#10，见最后一列）；其余 5 条无需提供任何材料，批准即可实施</t>
+          <t>PM 反馈已全部消化：#2 仅带量词触发+泰语纳入；#3 转通用标签模式集兜底（无需再提供样例，特殊格式后续遇到再精配）；#5 阈值 20 字；#7 仅全大写缩写、判严重；#10 转为文件内不混用检查</t>
         </is>
       </c>
     </row>
